--- a/Todolist.xlsx
+++ b/Todolist.xlsx
@@ -9,8 +9,12 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Pivot Table_Sheet1_2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <pivotCaches>
+    <pivotCache cacheId="1" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -20,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="116">
   <si>
     <t xml:space="preserve">Qui ?</t>
   </si>
@@ -58,6 +62,9 @@
     <t xml:space="preserve">creation des tables</t>
   </si>
   <si>
+    <t xml:space="preserve">Funaki</t>
+  </si>
+  <si>
     <t xml:space="preserve">donnees.sql</t>
   </si>
   <si>
@@ -67,9 +74,6 @@
     <t xml:space="preserve">inserer des donnees de teste</t>
   </si>
   <si>
-    <t xml:space="preserve">Funaki</t>
-  </si>
-  <si>
     <t xml:space="preserve">trouver un template</t>
   </si>
   <si>
@@ -103,6 +107,33 @@
     <t xml:space="preserve">mettre la connexion a la BDD</t>
   </si>
   <si>
+    <t xml:space="preserve">menu.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barre de menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mettre dans une page le menu commun des views</t>
+  </si>
+  <si>
+    <t xml:space="preserve">footer.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">footer des pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mettre dans une page le footer commun des views</t>
+  </si>
+  <si>
+    <t xml:space="preserve">header.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">header des pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mettre dans une page le header commun des views</t>
+  </si>
+  <si>
     <t xml:space="preserve">User.php</t>
   </si>
   <si>
@@ -199,6 +230,15 @@
     <t xml:space="preserve">créer une fonction getAllCategorie(), a l’aide de fecth vers ‘/api/getAll/categorie’</t>
   </si>
   <si>
+    <t xml:space="preserve">créer fonction add(data) , fecth vers ‘/api/add/categorie’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">créer fonction update(data), fecth vers ‘/api/update/categorie’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">créer fonction delet(id_categorie) , fecth vers ‘/api/delete/categorie/@id_categorie’</t>
+  </si>
+  <si>
     <t xml:space="preserve">met_objet.js</t>
   </si>
   <si>
@@ -208,28 +248,7 @@
     <t xml:space="preserve">créer une fonction getAllObjets(), a l’aide de fecth vers ‘/api/getAll/objet’</t>
   </si>
   <si>
-    <t xml:space="preserve">recupere objets filtrer par categorie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">créer une fonction getObjets(categorie), a l’aide de fecth ‘/api/getObjets’</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home.js</t>
-  </si>
-  <si>
-    <t xml:space="preserve">afficher les categories dans index.php</t>
-  </si>
-  <si>
-    <t xml:space="preserve">créer une fonction loadCategorie(), pour afficher les resultats de getAllCategorie()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">afficher les objets dans index.php</t>
-  </si>
-  <si>
-    <t xml:space="preserve">créer une fonction loadObjets() qui affiche la liste des objets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inscription.php</t>
+    <t xml:space="preserve">sign-in.php</t>
   </si>
   <si>
     <t xml:space="preserve">créer page inscription user</t>
@@ -238,15 +257,6 @@
     <t xml:space="preserve">formulaire d’inscription entant que ‘user’ : action : post vers ‘/add/user’</t>
   </si>
   <si>
-    <t xml:space="preserve">login_user.php</t>
-  </si>
-  <si>
-    <t xml:space="preserve">créer page login user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formulaire de login entant que ‘user’ : action : post vers ‘/login/user’</t>
-  </si>
-  <si>
     <t xml:space="preserve">url de inscription</t>
   </si>
   <si>
@@ -268,7 +278,13 @@
     <t xml:space="preserve">affiche la liste de tous ses objets ;il peut ajouter, enlever et modifier ses objets</t>
   </si>
   <si>
-    <t xml:space="preserve">lier chaque objet a sa page ‘/objet/@id_objet’</t>
+    <t xml:space="preserve">profile.js</t>
+  </si>
+  <si>
+    <t xml:space="preserve">script de profile.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">créer fonction loadObjets() pour afficher les objets de l’user connecter</t>
   </si>
   <si>
     <t xml:space="preserve">recupere objets filtrer par proprietaire</t>
@@ -301,34 +317,19 @@
     <t xml:space="preserve">marquer pour ‘/api/getObjets/@id_user’ =&gt; appel getObjets(id_user) de ObjetController</t>
   </si>
   <si>
-    <t xml:space="preserve">url de chaque objet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marquer pour ‘/objet/@id_objet’ =&gt; rediriger vers fiche_objet.php</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fiche_objet.php</t>
-  </si>
-  <si>
-    <t xml:space="preserve">detail d’un objet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">affiche les details de l’objet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proposition d’echange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">afficher la liste de tous les propositions d’echange avec l’objet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">profile.js</t>
-  </si>
-  <si>
-    <t xml:space="preserve">script de profile.php</t>
-  </si>
-  <si>
-    <t xml:space="preserve">créer fonction loadObjets() pour afficher les objets de l’user connecter</t>
+    <t xml:space="preserve">dashboard.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afficher les statistiques desusers, objets, echanges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ajout de nouveaux donnees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">donnees de teste pour les tables</t>
   </si>
   <si>
     <t xml:space="preserve">list_objets.php</t>
@@ -340,19 +341,37 @@
     <t xml:space="preserve">afficher la liste de tous les objets et son proprietaire =&gt; par script </t>
   </si>
   <si>
-    <t xml:space="preserve">list_objets.js</t>
-  </si>
-  <si>
-    <t xml:space="preserve">script de list_objets.php</t>
-  </si>
-  <si>
-    <t xml:space="preserve">créer fonction loadObjets() pour afficher les objets obtenus par getAllObjets()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">url de list_objets.php</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marquer pour ‘/list_objets’ =&gt; rediriger vers list_objets.php</t>
+    <t xml:space="preserve">gestion des categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afficher la liste de tous les categorie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rayan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page des utilisateurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afficher la liste de tous les utilisateurs : leur nom, email, tel, rôle, status, date d’inscription</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum - Temps p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum - Temps r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(empty)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Result</t>
   </si>
 </sst>
 </file>
@@ -363,7 +382,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00\ %"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -384,6 +403,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -407,7 +433,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="16">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -415,8 +441,113 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -440,8 +571,26 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -462,18 +611,92 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="12">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Pivot Table Category" xfId="20"/>
+    <cellStyle name="Pivot Table Corner" xfId="21"/>
+    <cellStyle name="Pivot Table Field" xfId="22"/>
+    <cellStyle name="Pivot Table Result" xfId="23"/>
+    <cellStyle name="Pivot Table Title" xfId="24"/>
+    <cellStyle name="Pivot Table Value" xfId="25"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -536,6 +759,971 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" recordCount="72" createdVersion="3">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:H58" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="Qui ?" numFmtId="0">
+      <sharedItems containsBlank="1" count="3">
+        <s v="Coralie"/>
+        <s v="Funaki"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Page" numFmtId="0">
+      <sharedItems containsBlank="1" count="24">
+        <s v="Categorie.php"/>
+        <s v="CategorieController.php"/>
+        <s v="config.php"/>
+        <s v="data.sql"/>
+        <s v="donnees.sql"/>
+        <s v="fiche_objet.php"/>
+        <s v="footer.php"/>
+        <s v="header.php"/>
+        <s v="home.js"/>
+        <s v="index.php"/>
+        <s v="list_objets.js"/>
+        <s v="list_objets.php"/>
+        <s v="login.php"/>
+        <s v="menu.php"/>
+        <s v="met_categorie.js"/>
+        <s v="met_objet.js"/>
+        <s v="Objet.php"/>
+        <s v="profile.js"/>
+        <s v="profile.php"/>
+        <s v="routes.php"/>
+        <s v="sign-in.php"/>
+        <s v="User.php"/>
+        <s v="UserController.php"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Type" numFmtId="0">
+      <sharedItems containsBlank="1" count="43">
+        <s v="add objet"/>
+        <s v="afficher les categories"/>
+        <s v="afficher les categories dans index.php"/>
+        <s v="afficher les objets dans index.php"/>
+        <s v="barre de menu"/>
+        <s v="configurer config.php"/>
+        <s v="creation base de donnees"/>
+        <s v="Creation controller de User.php"/>
+        <s v="creation de model Objet"/>
+        <s v="creation de model User"/>
+        <s v="créer controller de Categorie"/>
+        <s v="créer page inscription user"/>
+        <s v="créer un model Categorie"/>
+        <s v="delete objet"/>
+        <s v="detail d’un objet"/>
+        <s v="filtrer objets par categorie"/>
+        <s v="fonction login"/>
+        <s v="footer des pages"/>
+        <s v="header des pages"/>
+        <s v="insertion de donnees"/>
+        <s v="integration"/>
+        <s v="mis en place MVC"/>
+        <s v="page de tous les objets"/>
+        <s v="page login admin"/>
+        <s v="page objet user"/>
+        <s v="proposition d’echange"/>
+        <s v="recuperation des categories"/>
+        <s v="recuperation des tous objets"/>
+        <s v="recupere objets filtrer par categorie"/>
+        <s v="recupere objets filtrer par proprietaire"/>
+        <s v="renommer les fichiers"/>
+        <s v="script de list_objets.php"/>
+        <s v="script de profile.php"/>
+        <s v="trouver un template"/>
+        <s v="update objet"/>
+        <s v="url de chaque objet"/>
+        <s v="url de inscription"/>
+        <s v="url de la page d’accueil"/>
+        <s v="url de list_objets.php"/>
+        <s v="url de login"/>
+        <s v="url de login_user"/>
+        <s v="url de objet"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Description" numFmtId="0">
+      <sharedItems containsBlank="1" count="46">
+        <s v="affiche la liste de tous ses objets ;il peut ajouter, enlever et modifier ses objets"/>
+        <s v="affiche les details de l’objet"/>
+        <s v="afficher la liste de tous les objets et son proprietaire =&gt; par script "/>
+        <s v="afficher la liste de tous les propositions d’echange avec l’objet"/>
+        <s v="creation des dossiers et fichier scructure MVC"/>
+        <s v="creation des tables"/>
+        <s v="créer fonction add(data) , fecth vers ‘/api/add/categorie’"/>
+        <s v="créer fonction addObjet(), avec fetch ‘/api/add/objet’"/>
+        <s v="créer fonction delet(id_categorie) , fecth vers ‘/api/delete/categorie/@id_categorie’"/>
+        <s v="créer fonction deleteObjet(), avec fetch ‘/api/delete/objet’"/>
+        <s v="créer fonction loadObjets() pour afficher les objets de l’user connecter"/>
+        <s v="créer fonction loadObjets() pour afficher les objets obtenus par getAllObjets()"/>
+        <s v="créer fonction update(data), fecth vers ‘/api/update/categorie’"/>
+        <s v="créer fonction updateObjet(), avec fetch ‘/api/update/objet’"/>
+        <s v="créer les fonctionc insert, update, delete, get"/>
+        <s v="créer les fonctions qui appelent Categorie model"/>
+        <s v="créer les fonctions qui font appel au User model"/>
+        <s v="créer un formulaire de login pour admin =&gt; action:post vers ‘/login/admin’"/>
+        <s v="créer un script pour recevoir la liste des categorie (implementer le script)"/>
+        <s v="créer une fonction getAllCategorie(), a l’aide de fecth vers ‘/api/getAll/categorie’"/>
+        <s v="créer une fonction getAllObjets(), a l’aide de fecth vers ‘/api/getAll/objet’"/>
+        <s v="créer une fonction getObjets(categorie), a l’aide de fecth ‘/api/getObjets’"/>
+        <s v="créer une fonction getUserObjet() , avec fetch ‘/api/getObjets/@id_user’"/>
+        <s v="créer une fonction loadCategorie(), pour afficher les resultats de getAllCategorie()"/>
+        <s v="créer une fonction loadObjets() qui affiche la liste des objets"/>
+        <s v="formulaire d’inscription entant que ‘user’ : action : post vers ‘/add/user’"/>
+        <s v="inserer des donnees de teste"/>
+        <s v="integrer template a MVC"/>
+        <s v="lier chaque objet a sa page ‘/objet/@id_objet’"/>
+        <s v="marquer pour ‘/api/getObjets/@id_user’ =&gt; appel getObjets(id_user) de ObjetController"/>
+        <s v="marquer pour ‘/list_objets’ =&gt; rediriger vers list_objets.php"/>
+        <s v="marquer pour ‘/login/user’ =&gt; appel de la fonction login() de UserController"/>
+        <s v="marquer pour ‘/objet/@id_objet’ =&gt; rediriger vers fiche_objet.php"/>
+        <s v="marquer pour get ‘/’ =&gt; login.php"/>
+        <s v="marquer pour get’/home’ =&gt; index.php"/>
+        <s v="marquer pour post ‘/add/user’ =&gt; appel la fonction insert() de UserController"/>
+        <s v="marquer pour post ‘/login/admin’ =&gt; appel la fonction login() de UserController"/>
+        <s v="mettre dans une page le footer commun des views"/>
+        <s v="mettre dans une page le header commun des views"/>
+        <s v="mettre dans une page le menu commun des views"/>
+        <s v="mettre la connexion a la BDD"/>
+        <s v="mettre tous les .html en php"/>
+        <s v="prendre un template gratuit pour demarer"/>
+        <s v="une liste deroulante des categories"/>
+        <s v="verifie si user existe ;procede a la connexion (admin :vers ‘/home’)  (user : vers ’/profile’)"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Estimation" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="20" count="7">
+        <n v="3"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="10"/>
+        <n v="15"/>
+        <n v="20"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Temps p" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="15" count="7">
+        <n v="3"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="8"/>
+        <n v="10"/>
+        <n v="15"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Temps r" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="10" count="6">
+        <n v="0"/>
+        <n v="1"/>
+        <n v="2"/>
+        <n v="5"/>
+        <n v="10"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Avancement" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="0.5" maxValue="1" count="10">
+        <n v="0.5"/>
+        <n v="0.666666666666667"/>
+        <n v="0.75"/>
+        <n v="0.833333333333333"/>
+        <n v="0.857142857142857"/>
+        <n v="0.888888888888889"/>
+        <n v="0.909090909090909"/>
+        <n v="1"/>
+        <e v="#DIV/0!"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="72">
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="19"/>
+    <x v="26"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="33"/>
+    <x v="42"/>
+    <x v="5"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="21"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="20"/>
+    <x v="27"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="30"/>
+    <x v="41"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="40"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="4"/>
+    <x v="39"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="17"/>
+    <x v="37"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="18"/>
+    <x v="38"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="9"/>
+    <x v="14"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="8"/>
+    <x v="14"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="7"/>
+    <x v="16"/>
+    <x v="4"/>
+    <x v="5"/>
+    <x v="3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="16"/>
+    <x v="44"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="23"/>
+    <x v="17"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="19"/>
+    <x v="39"/>
+    <x v="33"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="36"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="19"/>
+    <x v="37"/>
+    <x v="34"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="14"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="15"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="15"/>
+    <x v="43"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="26"/>
+    <x v="19"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="12"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="27"/>
+    <x v="20"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="28"/>
+    <x v="21"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="8"/>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="11"/>
+    <x v="25"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="19"/>
+    <x v="36"/>
+    <x v="35"/>
+    <x v="2"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="40"/>
+    <x v="31"/>
+    <x v="2"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="18"/>
+    <x v="24"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="28"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="15"/>
+    <x v="29"/>
+    <x v="22"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="34"/>
+    <x v="13"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="13"/>
+    <x v="9"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="19"/>
+    <x v="41"/>
+    <x v="29"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="35"/>
+    <x v="32"/>
+    <x v="2"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="14"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="25"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="17"/>
+    <x v="32"/>
+    <x v="10"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="22"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="31"/>
+    <x v="11"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="23"/>
+    <x v="42"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="19"/>
+    <x v="38"/>
+    <x v="30"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="8"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="DataPilot2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="0" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="0" outlineData="0" compact="0" compactData="0">
+  <location ref="A1:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField axis="axisRow" compact="0" showAll="0" defaultSubtotal="0" outline="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" showAll="0" outline="0"/>
+    <pivotField dataField="1" compact="0" showAll="0" outline="0"/>
+    <pivotField compact="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="0"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x v="3"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="1">
+    <i t="grand">
+      <x v="0"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum - Temps p" fld="5" subtotal="sum" numFmtId="164"/>
+    <dataField name="Sum - Temps r" fld="6" subtotal="sum" numFmtId="164"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -649,7 +1837,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.78"/>
@@ -717,15 +1905,17 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>10</v>
@@ -744,7 +1934,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
@@ -761,7 +1951,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
@@ -786,7 +1976,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
@@ -811,7 +2001,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
@@ -836,7 +2026,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
@@ -864,8 +2054,10 @@
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
       <c r="H11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -875,199 +2067,264 @@
       <c r="B12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="H12" s="4" t="e">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
         <f aca="false">F12/(F12+G12)</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="D13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <f aca="false">F13/(F13+G13)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="H14" s="4" t="e">
+        <v>35</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <f aca="false">F14/(F14+G14)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
       <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H16" s="4" t="e">
+      <c r="F16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" s="4" t="n">
         <f aca="false">F16/(F16+G16)</f>
-        <v>#DIV/0!</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="1" t="n">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="H17" s="4" t="e">
-        <f aca="false">F17/(F17+G17)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="F18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <f aca="false">F18/(F18+G18)</f>
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D19" s="3"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="3" t="n">
+      <c r="F20" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="H19" s="4" t="e">
-        <f aca="false">F19/(F19+G19)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="H20" s="4"/>
+      <c r="G20" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <f aca="false">F20/(F20+G20)</f>
+        <v>0.75</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
-      <c r="B21" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="B21" s="3"/>
       <c r="C21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E21" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H21" s="4" t="e">
+      <c r="G21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="4" t="n">
         <f aca="false">F21/(F21+G21)</f>
-        <v>#DIV/0!</v>
+        <v>0.833333333333333</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
-      <c r="D22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" s="4" t="e">
-        <f aca="false">F22/(F22+G22)</f>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="H23" s="4" t="e">
+        <f aca="false">F23/(F23+G23)</f>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="H23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
-      <c r="B24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" s="4" t="e">
-        <f aca="false">F24/(F24+G24)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="H25" s="4"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="B25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" s="4" t="e">
+        <f aca="false">F25/(F25+G25)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3"/>
       <c r="D26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>15</v>
+        <v>52</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="H26" s="4" t="e">
         <f aca="false">F26/(F26+G26)</f>
@@ -1075,22 +2332,24 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="3"/>
+      <c r="A27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
       <c r="H27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
-      <c r="B28" s="3" t="s">
-        <v>48</v>
+      <c r="B28" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H28" s="4" t="e">
         <f aca="false">F28/(F28+G28)</f>
@@ -1099,83 +2358,102 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3" t="s">
-        <v>51</v>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <f aca="false">F30/(F30+G30)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="3"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <f aca="false">F32/(F32+G32)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="4" t="e">
-        <f aca="false">F30/(F30+G30)</f>
+      <c r="H34" s="4" t="e">
+        <f aca="false">F34/(F34+G34)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C31" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H31" s="4" t="e">
-        <f aca="false">F31/(F31+G31)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H33" s="4" t="e">
-        <f aca="false">F33/(F33+G33)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="3" t="s">
-        <v>59</v>
-      </c>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E35" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>10</v>
       </c>
       <c r="H35" s="4" t="e">
@@ -1183,109 +2461,147 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E36" s="3" t="n">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H36" s="4" t="e">
-        <f aca="false">F36/(F36+G36)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E37" s="3"/>
-      <c r="H37" s="4"/>
+      <c r="F37" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <f aca="false">F37/(F37+G37)</f>
+        <v>0.75</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E38" s="3" t="n">
+      <c r="A38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H38" s="4" t="e">
+      <c r="F38" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="4" t="n">
         <f aca="false">F38/(F38+G38)</f>
-        <v>#DIV/0!</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>68</v>
+      <c r="A39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H39" s="4" t="e">
+      <c r="F39" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="4" t="n">
         <f aca="false">F39/(F39+G39)</f>
-        <v>#DIV/0!</v>
+        <v>0.888888888888889</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="H40" s="4"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C41" s="1" t="s">
+      <c r="A40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E40" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <f aca="false">F40/(F40+G40)</f>
+        <v>0.888888888888889</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="H41" s="4" t="e">
-        <f aca="false">F41/(F41+G41)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <f aca="false">F42/(F42+G42)</f>
+        <v>0.909090909090909</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="H42" s="4" t="e">
-        <f aca="false">F42/(F42+G42)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H43" s="4"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>75</v>
@@ -1294,7 +2610,7 @@
         <v>76</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H44" s="4" t="e">
         <f aca="false">F44/(F44+G44)</f>
@@ -1302,35 +2618,41 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C45" s="1" t="s">
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E46" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H45" s="4" t="e">
-        <f aca="false">F45/(F45+G45)</f>
+      <c r="H46" s="4" t="e">
+        <f aca="false">F46/(F46+G46)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H46" s="4"/>
-    </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="1" t="s">
+      <c r="A47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="E47" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H47" s="4" t="e">
         <f aca="false">F47/(F47+G47)</f>
@@ -1338,26 +2660,41 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D48" s="5" t="s">
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D49" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>15</v>
+      </c>
       <c r="H49" s="4" t="e">
         <f aca="false">F49/(F49+G49)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="B50" s="1" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>15</v>
@@ -1368,29 +2705,26 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C51" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="H51" s="4" t="e">
         <f aca="false">F51/(F51+G51)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="C52" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="5" t="s">
         <v>88</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H52" s="4" t="e">
         <f aca="false">F52/(F52+G52)</f>
@@ -1398,6 +2732,9 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="C53" s="1" t="s">
         <v>89</v>
       </c>
@@ -1413,17 +2750,32 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H54" s="4"/>
+      <c r="A54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="H54" s="4" t="e">
+        <f aca="false">F54/(F54+G54)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="1" t="s">
-        <v>40</v>
+      <c r="A55" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>10</v>
@@ -1434,150 +2786,125 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C56" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E56" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H56" s="4" t="e">
-        <f aca="false">F56/(F56+G56)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="H56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="H57" s="4" t="e">
         <f aca="false">F57/(F57+G57)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="H58" s="4" t="e">
         <f aca="false">F58/(F58+G58)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="C59" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E59" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="H59" s="4" t="e">
-        <f aca="false">F59/(F59+G59)</f>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" s="4" t="e">
+        <f aca="false">F64/(F64+G64)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H60" s="4"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="H61" s="4" t="e">
-        <f aca="false">F61/(F61+G61)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H62" s="4"/>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D63" s="1" t="s">
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E63" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H63" s="4" t="e">
-        <f aca="false">F63/(F63+G63)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H64" s="4"/>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B65" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="H66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E65" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H65" s="4" t="e">
-        <f aca="false">F65/(F65+G65)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H66" s="4"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B67" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C67" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E67" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H67" s="4" t="e">
-        <f aca="false">F67/(F67+G67)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="H68" s="4"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D48" r:id="rId1" display="lier chaque objet a sa page ‘/objet/@id_objet’"/>
-    <hyperlink ref="D50" r:id="rId2" display="créer une fonction getUserObjet() , avec fetch ‘/api/getObjets/@id_user’"/>
-    <hyperlink ref="D55" r:id="rId3" display="marquer pour ‘/api/getObjets/@id_user’ =&gt; appel getObjets(id_user) de ObjetController"/>
-    <hyperlink ref="D56" r:id="rId4" display="marquer pour ‘/objet/@id_objet’ =&gt; rediriger vers fiche_objet.php"/>
+    <hyperlink ref="D40" r:id="rId1" display="créer fonction delet(id_categorie) , fecth vers ‘/api/delete/categorie/@id_categorie’"/>
+    <hyperlink ref="D52" r:id="rId2" display="créer une fonction getUserObjet() , avec fetch ‘/api/getObjets/@id_user’"/>
+    <hyperlink ref="D57" r:id="rId3" display="marquer pour ‘/api/getObjets/@id_user’ =&gt; appel getObjets(id_user) de ObjetController"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -1587,4 +2914,108 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.07"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <f aca="false">B3/(B3+C3)</f>
+        <v>0.821428571428571</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <f aca="false">B4/(B4+C4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <f aca="false">B5/(B5+C5)</f>
+        <v>0.833333333333333</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="21" t="n">
+        <v>160</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <f aca="false">B6/(B6+C6)</f>
+        <v>0.847457627118644</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>